--- a/resources/templates/standard/K2100-09.xlsx
+++ b/resources/templates/standard/K2100-09.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>소모품 사양 및 공급처 지정 현황</t>
   </si>
@@ -574,12 +577,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -620,15 +625,15 @@
       <c r="AP1" s="2"/>
       <c r="AQ1" s="2"/>
       <c r="AR1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT1" s="4"/>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW1" s="4"/>
       <c r="AX1" s="4"/>
@@ -739,17 +744,17 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -760,7 +765,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
@@ -771,7 +776,7 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
@@ -782,7 +787,7 @@
       <c r="AF4" s="4"/>
       <c r="AG4" s="4"/>
       <c r="AH4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
@@ -793,7 +798,7 @@
       <c r="AO4" s="4"/>
       <c r="AP4" s="4"/>
       <c r="AQ4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR4" s="4"/>
       <c r="AS4" s="4"/>
@@ -1021,7 +1026,7 @@
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -1075,7 +1080,7 @@
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
